--- a/www/download/IND.gross_output.s.mv.rpA1.xlsx
+++ b/www/download/IND.gross_output.s.mv.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17386.895</t>
+          <t>17386895122.6289</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17682.083</t>
+          <t>17682083254.6346</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17678.528</t>
+          <t>17678528324.0997</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17667.467</t>
+          <t>17667466533.8696</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18689.92</t>
+          <t>18689920038.3605</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18055.665</t>
+          <t>18055665259.5568</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17506.793</t>
+          <t>17506793208.004</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18402.728</t>
+          <t>18402727716.2333</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19284.992</t>
+          <t>19284991662.7074</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21553.014</t>
+          <t>21553013897.4174</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22033.367</t>
+          <t>22033367044.6177</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22405.327</t>
+          <t>22405326823.3011</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>23520.351</t>
+          <t>23520350556.5103</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>24621.851</t>
+          <t>24621851394.1385</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>25159.792</t>
+          <t>25159791681.8096</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9345.724</t>
+          <t>9345724358.52914</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9601.809</t>
+          <t>9601809039.9147</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8974.217</t>
+          <t>8974216706.09635</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9188.01</t>
+          <t>9188010222.8701</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9232.266</t>
+          <t>9232266173.72242</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9670.591</t>
+          <t>9670591145.13236</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9818.732</t>
+          <t>9818732080.80058</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9558.109</t>
+          <t>9558108625.92395</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9886.48</t>
+          <t>9886479888.12849</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10212.736</t>
+          <t>10212735741.3108</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10072.033</t>
+          <t>10072033224.5569</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10858.162</t>
+          <t>10858162278.1807</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>11168.639</t>
+          <t>11168639190.7962</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10293.085</t>
+          <t>10293085362.0512</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>8799.273</t>
+          <t>8799272591.00579</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11796.603</t>
+          <t>11796603407.5345</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11138.413</t>
+          <t>11138413028.8153</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10599.2</t>
+          <t>10599199577.4446</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10776.756</t>
+          <t>10776756328.1199</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10956.309</t>
+          <t>10956309221.3061</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11902.348</t>
+          <t>11902348134.8057</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11871.224</t>
+          <t>11871224148.9543</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11498.31</t>
+          <t>11498309840.829</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12398.501</t>
+          <t>12398501198.5379</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13184.423</t>
+          <t>13184423276.1027</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12692.943</t>
+          <t>12692942742.1493</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13673.424</t>
+          <t>13673423677.3605</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14224.53</t>
+          <t>14224530164.3092</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>16585.212</t>
+          <t>16585211701.482</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>12441.182</t>
+          <t>12441182171.7545</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7704.266</t>
+          <t>7704265832.55644</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8104.99</t>
+          <t>8104990241.72075</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7378.473</t>
+          <t>7378473242.05349</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7011.829</t>
+          <t>7011829361.32707</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6544.278</t>
+          <t>6544278466.23565</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6167.446</t>
+          <t>6167445955.0294</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5945.517</t>
+          <t>5945516982.55316</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5813.806</t>
+          <t>5813805990.65744</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5994.749</t>
+          <t>5994749218.18958</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6394.043</t>
+          <t>6394043107.64283</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6547.86</t>
+          <t>6547860470.26004</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6949.687</t>
+          <t>6949686509.63272</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7186.241</t>
+          <t>7186241148.81653</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7210.144</t>
+          <t>7210143607.9678</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7209.443</t>
+          <t>7209442679.56756</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>158691.117</t>
+          <t>158691116610.613</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>156306.106</t>
+          <t>156306106098.581</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>155617.768</t>
+          <t>155617768360.309</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>151837.635</t>
+          <t>151837634831.283</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>155548.752</t>
+          <t>155548752250.732</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>159852.487</t>
+          <t>159852486591.213</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>155776.481</t>
+          <t>155776480658.308</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>161339.12</t>
+          <t>161339119796.566</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165788.344</t>
+          <t>165788344336.218</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>174322.63</t>
+          <t>174322629680.701</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>177931.293</t>
+          <t>177931293437.987</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>175406.261</t>
+          <t>175406260918.412</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>177282.547</t>
+          <t>177282547360.451</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>181637.842</t>
+          <t>181637841750.595</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>175210.62</t>
+          <t>175210620374.908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27537.887</t>
+          <t>27537886708.0814</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28030.771</t>
+          <t>28030771220.8669</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27774.656</t>
+          <t>27774656353.644</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28073.532</t>
+          <t>28073531863.4062</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29701.362</t>
+          <t>29701362063.8601</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32636.404</t>
+          <t>32636404239.392</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>32857.327</t>
+          <t>32857327487.3107</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31637.304</t>
+          <t>31637304015.0578</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>32894.556</t>
+          <t>32894555558.9339</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>35999.639</t>
+          <t>35999638655.909</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>36991.481</t>
+          <t>36991481084.7448</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>38095.613</t>
+          <t>38095612838.5434</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>36891.526</t>
+          <t>36891526100.1928</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>37368.254</t>
+          <t>37368253964.3973</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>34353.866</t>
+          <t>34353866082.4595</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1943002.995</t>
+          <t>1943002995087.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1995348.722</t>
+          <t>1995348721891.84</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2007207.142</t>
+          <t>2007207141713.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1985688.774</t>
+          <t>1985688774324.43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1960371.405</t>
+          <t>1960371405179.8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1931302.959</t>
+          <t>1931302959421.86</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1961402.07</t>
+          <t>1961402070155.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1994455.008</t>
+          <t>1994455008177.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2109504.577</t>
+          <t>2109504577197.74</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2160355.8</t>
+          <t>2160355800498.64</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2271850.823</t>
+          <t>2271850823478.65</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2492583.469</t>
+          <t>2492583468752.92</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2598260.28</t>
+          <t>2598260279632.21</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2699937.587</t>
+          <t>2699937587283.73</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2735917.867</t>
+          <t>2735917866656.93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>602.809</t>
+          <t>602808928.412623</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>658.847</t>
+          <t>658846902.521193</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>583.979</t>
+          <t>583978731.761368</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>590.181</t>
+          <t>590181315.020602</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>644.239</t>
+          <t>644238961.348876</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>633.095</t>
+          <t>633094541.432591</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>699.294</t>
+          <t>699293740.250372</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>720.78</t>
+          <t>720780411.686187</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>748.043</t>
+          <t>748042892.383591</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>710.978</t>
+          <t>710978189.338023</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>647.379</t>
+          <t>647378752.698181</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>665.008</t>
+          <t>665007523.233878</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>642.247</t>
+          <t>642246749.953578</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>890.354</t>
+          <t>890353574.102561</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>588.486</t>
+          <t>588486256.870858</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13540.883</t>
+          <t>13540882646.5856</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13873.14</t>
+          <t>13873139961.3047</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14192.417</t>
+          <t>14192416671.9179</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13593.374</t>
+          <t>13593374417.2392</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13048.522</t>
+          <t>13048521510.6449</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12505.747</t>
+          <t>12505746862.2655</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12818.769</t>
+          <t>12818768881.7147</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12959.668</t>
+          <t>12959668337.475</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12896.135</t>
+          <t>12896134941.6622</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13225.206</t>
+          <t>13225205866.1919</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>13216.855</t>
+          <t>13216855400.689</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>14203.813</t>
+          <t>14203813151.9468</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>14760.565</t>
+          <t>14760564848.2425</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14260.811</t>
+          <t>14260811095.5921</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11833.646</t>
+          <t>11833645781.4649</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>86002.333</t>
+          <t>86002332799.9248</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79510.251</t>
+          <t>79510250987.1284</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75495.312</t>
+          <t>75495312221.5423</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78578.073</t>
+          <t>78578073352.1759</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>79213.561</t>
+          <t>79213560537.098</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>83651.07</t>
+          <t>83651069597.4169</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>79709.111</t>
+          <t>79709111287.8876</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77150.904</t>
+          <t>77150904151.5502</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>82236.303</t>
+          <t>82236303175.8609</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>85786.867</t>
+          <t>85786866785.4624</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>84748.729</t>
+          <t>84748728573.7513</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>89736.727</t>
+          <t>89736727228.4953</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>93999.499</t>
+          <t>93999499282.4312</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>84043.816</t>
+          <t>84043815568.0473</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>69986.683</t>
+          <t>69986683093.3725</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7177.503</t>
+          <t>7177503237.47842</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7111.921</t>
+          <t>7111920868.266</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7479.513</t>
+          <t>7479512787.9245</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6864.353</t>
+          <t>6864353339.71057</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6434.922</t>
+          <t>6434921568.14435</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6513.323</t>
+          <t>6513323423.01306</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6669.451</t>
+          <t>6669451270.01401</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6529.867</t>
+          <t>6529867416.61943</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6928.405</t>
+          <t>6928404787.2289</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7086.07</t>
+          <t>7086069564.49621</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6921.36</t>
+          <t>6921359817.00651</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7066.632</t>
+          <t>7066632306.94758</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7219.343</t>
+          <t>7219343030.16132</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6675.1</t>
+          <t>6675100137.51316</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5664.677</t>
+          <t>5664677263.28354</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32789.266</t>
+          <t>32789265756.398</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32809.328</t>
+          <t>32809327638.8819</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31375.826</t>
+          <t>31375826455.3755</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33462.424</t>
+          <t>33462424244.3801</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>36101.247</t>
+          <t>36101247362.3954</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>38911.35</t>
+          <t>38911349561.2398</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>39401.711</t>
+          <t>39401711351.2018</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41353.524</t>
+          <t>41353523571.1772</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42384.411</t>
+          <t>42384410799.2424</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44487.291</t>
+          <t>44487290503.7638</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46492.486</t>
+          <t>46492485614.9848</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48480.523</t>
+          <t>48480523102.0369</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49768.172</t>
+          <t>49768171575.7432</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46686.688</t>
+          <t>46686687643.8797</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>36886.41</t>
+          <t>36886409591.0312</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1432.066</t>
+          <t>1432065891.90805</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1384.266</t>
+          <t>1384265735.9432</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1444.538</t>
+          <t>1444538230.21735</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1471.272</t>
+          <t>1471271552.83167</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1364.366</t>
+          <t>1364365644.87959</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1468.711</t>
+          <t>1468710772.69898</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1588.26</t>
+          <t>1588260011.01194</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1667.877</t>
+          <t>1667876809.84553</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1769.693</t>
+          <t>1769692736.88119</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1885.797</t>
+          <t>1885797495.44548</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1742.976</t>
+          <t>1742976095.55094</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1786.424</t>
+          <t>1786424054.74167</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1661.53</t>
+          <t>1661529823.14881</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1592.359</t>
+          <t>1592358679.12429</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1293.876</t>
+          <t>1293875738.77076</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6717.255</t>
+          <t>6717255368.38918</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6597.238</t>
+          <t>6597238238.88994</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6429.136</t>
+          <t>6429135638.83179</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6839.987</t>
+          <t>6839987420.07982</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7240.457</t>
+          <t>7240457144.52789</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7279.794</t>
+          <t>7279794240.19296</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6964.996</t>
+          <t>6964995797.95902</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6879.373</t>
+          <t>6879372720.20278</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7229.551</t>
+          <t>7229550754.76425</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7429.944</t>
+          <t>7429943756.37025</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7667.354</t>
+          <t>7667354336.14852</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8025.579</t>
+          <t>8025579468.9062</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>8171.624</t>
+          <t>8171624262.67934</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>7656.679</t>
+          <t>7656678623.25369</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5668.044</t>
+          <t>5668043635.38076</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48868.475</t>
+          <t>48868474943.7432</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47733.34</t>
+          <t>47733340472.9938</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43551.535</t>
+          <t>43551534666.2684</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45173.473</t>
+          <t>45173473120.8609</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>47781.17</t>
+          <t>47781169988.2868</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>49442.377</t>
+          <t>49442377374.9714</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>49137.303</t>
+          <t>49137303099.4335</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>47526.531</t>
+          <t>47526531388.0201</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>49468.689</t>
+          <t>49468689438.0168</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>51025.996</t>
+          <t>51025996220.8201</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>51644.379</t>
+          <t>51644378694.5016</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>52297.538</t>
+          <t>52297538307.5937</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>53761.892</t>
+          <t>53761892121.5491</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>49851.486</t>
+          <t>49851486350.3217</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>43683.259</t>
+          <t>43683258842.2592</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>51648.76</t>
+          <t>51648760072.0461</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52292.527</t>
+          <t>52292527039.6493</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50244.19</t>
+          <t>50244190362.3571</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50074.114</t>
+          <t>50074114462.0081</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>49525.017</t>
+          <t>49525016863.2939</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>48808.677</t>
+          <t>48808677454.9439</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47832.68</t>
+          <t>47832680470.1959</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46649.529</t>
+          <t>46649528631.2782</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47197.401</t>
+          <t>47197401495.0977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48973.449</t>
+          <t>48973449359.475</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>49956.998</t>
+          <t>49956997527.2247</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>50443.253</t>
+          <t>50443252896.0992</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>50477.65</t>
+          <t>50477649593.2265</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>44826.639</t>
+          <t>44826638717.1299</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40188.288</t>
+          <t>40188288386.4937</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9821.765</t>
+          <t>9821764671.57857</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10091.57</t>
+          <t>10091569699.6901</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9295.043</t>
+          <t>9295043338.24446</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9252.568</t>
+          <t>9252568101.3012</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9282.321</t>
+          <t>9282321016.8407</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10034.817</t>
+          <t>10034817080.6935</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9542.076</t>
+          <t>9542075916.01469</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9542.804</t>
+          <t>9542803697.2875</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9503.953</t>
+          <t>9503953000.05516</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9301.471</t>
+          <t>9301470651.88168</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9296.602</t>
+          <t>9296602047.35015</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9950.66</t>
+          <t>9950659905.84512</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9991.433</t>
+          <t>9991433010.22957</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10053.543</t>
+          <t>10053543009.3824</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9169.763</t>
+          <t>9169763390.06976</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10687.048</t>
+          <t>10687048098.7529</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10580.868</t>
+          <t>10580867595.8651</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10108.096</t>
+          <t>10108096174.6282</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10305.794</t>
+          <t>10305794216.8176</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11057.979</t>
+          <t>11057979441.4603</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10943.115</t>
+          <t>10943115323.1188</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10631.916</t>
+          <t>10631916293.9736</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10601.283</t>
+          <t>10601282819.0964</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10575.475</t>
+          <t>10575475071.0039</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10004.125</t>
+          <t>10004125087.9344</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9854.714</t>
+          <t>9854713981.81513</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9899.104</t>
+          <t>9899103736.89402</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10126.637</t>
+          <t>10126636890.464</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9009.285</t>
+          <t>9009284597.76986</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8052.975</t>
+          <t>8052974534.17578</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>140408.758</t>
+          <t>140408758499.751</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>145739.498</t>
+          <t>145739497609.845</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>141603.09</t>
+          <t>141603090181.534</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>132851.521</t>
+          <t>132851521427.75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>151034.009</t>
+          <t>151034009095.324</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>159377.755</t>
+          <t>159377755140.334</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>163014.549</t>
+          <t>163014548636.888</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>173597.844</t>
+          <t>173597844307.903</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>179749.533</t>
+          <t>179749532800.466</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>177958.757</t>
+          <t>177958757047.086</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>158021.337</t>
+          <t>158021336582.946</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>152566.466</t>
+          <t>152566466200.504</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>158754.976</t>
+          <t>158754976380.612</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>162194.187</t>
+          <t>162194186513.12</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>170799.794</t>
+          <t>170799794422.201</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1195298.544</t>
+          <t>1195298543963.4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1213484.126</t>
+          <t>1213484125931.65</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1232635.988</t>
+          <t>1232635987900.24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1224819.75</t>
+          <t>1224819749877.59</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1190208.715</t>
+          <t>1190208714742.81</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1237590.744</t>
+          <t>1237590743996.34</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1279651.546</t>
+          <t>1279651546303.09</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1252110.715</t>
+          <t>1252110715339.01</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1347662.752</t>
+          <t>1347662752204.2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1376004.651</t>
+          <t>1376004650617.89</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1404446.196</t>
+          <t>1404446196023.77</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1419141.979</t>
+          <t>1419141978938.4</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1383375.885</t>
+          <t>1383375885210.4</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1373413.242</t>
+          <t>1373413241646.2</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1404440.93</t>
+          <t>1404440929974.65</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4452.551</t>
+          <t>4452550759.42778</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4556.169</t>
+          <t>4556169011.7283</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4440.938</t>
+          <t>4440937726.25234</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4405.043</t>
+          <t>4405042565.32921</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4839.926</t>
+          <t>4839925530.39126</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5141.846</t>
+          <t>5141846036.04709</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5249.747</t>
+          <t>5249746983.22547</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4967.22</t>
+          <t>4967220096.59107</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5289.275</t>
+          <t>5289275318.42818</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5800.425</t>
+          <t>5800425495.64622</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6100.02</t>
+          <t>6100019601.01375</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6350.985</t>
+          <t>6350984773.54642</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6637.688</t>
+          <t>6637687958.12643</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5785.121</t>
+          <t>5785121119.68979</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5089.062</t>
+          <t>5089062173.66419</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>58988.96</t>
+          <t>58988959829.3337</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>58706.774</t>
+          <t>58706773713.9007</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55695.642</t>
+          <t>55695641911.4341</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>57566.328</t>
+          <t>57566327647.5397</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>58287.153</t>
+          <t>58287153328.925</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>61281.041</t>
+          <t>61281041366.2717</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>60975.957</t>
+          <t>60975957161.6957</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>60497.841</t>
+          <t>60497840559.3512</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>62933.37</t>
+          <t>62933370340.0244</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>65643.137</t>
+          <t>65643137265.5088</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>64867.109</t>
+          <t>64867108587.5006</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69518.554</t>
+          <t>69518553530.2845</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>70070.251</t>
+          <t>70070250783.0506</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>62286.295</t>
+          <t>62286295077.7557</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>50518.775</t>
+          <t>50518774715.7566</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>204556.314</t>
+          <t>204556314462.537</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>194948.289</t>
+          <t>194948289050.517</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>187603.517</t>
+          <t>187603516841.049</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>169328.336</t>
+          <t>169328335771.487</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>172622.261</t>
+          <t>172622261081.729</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>181321.618</t>
+          <t>181321617841.408</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>174224.077</t>
+          <t>174224077067.418</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>165973.184</t>
+          <t>165973184007.73</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>171915.107</t>
+          <t>171915107184.752</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>180440.958</t>
+          <t>180440957514.792</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>180618.979</t>
+          <t>180618978891.244</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>185442.129</t>
+          <t>185442128841.815</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>183482.115</t>
+          <t>183482115440.916</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>190679.468</t>
+          <t>190679467814.859</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>160859.575</t>
+          <t>160859574541.342</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>82855.312</t>
+          <t>82855312076.1908</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>83117.096</t>
+          <t>83117095608.1248</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81621.534</t>
+          <t>81621534455.8094</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69542.037</t>
+          <t>69542036597.6117</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75388.533</t>
+          <t>75388532833.8487</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>81245.8</t>
+          <t>81245800072.2372</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>78979.348</t>
+          <t>78979347688.6637</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80462.901</t>
+          <t>80462900677.2937</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>82958.72</t>
+          <t>82958719990.6911</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>89646.514</t>
+          <t>89646513535.2384</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>89730.616</t>
+          <t>89730615679.3667</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>94077.891</t>
+          <t>94077891245.7855</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>94257.104</t>
+          <t>94257103885.9692</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>97040.004</t>
+          <t>97040004432.9099</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>88964.014</t>
+          <t>88964013500.651</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3249.856</t>
+          <t>3249855642.20138</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3169.452</t>
+          <t>3169451546.10514</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2853.462</t>
+          <t>2853461661.98951</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3043.99</t>
+          <t>3043989662.72564</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2884.569</t>
+          <t>2884569396.15666</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2936.208</t>
+          <t>2936208239.32385</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2881.868</t>
+          <t>2881868028.41997</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2920.627</t>
+          <t>2920627275.162</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3020.081</t>
+          <t>3020081120.71029</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2867.222</t>
+          <t>2867222454.00816</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3018.836</t>
+          <t>3018836020.07636</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2983.099</t>
+          <t>2983099243.42681</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3038.979</t>
+          <t>3038979115.08717</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3194.708</t>
+          <t>3194708116.36327</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2740.563</t>
+          <t>2740563116.59499</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>482.748</t>
+          <t>482747916.586769</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>428.814</t>
+          <t>428813523.139351</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>402.608</t>
+          <t>402608068.317656</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>434.388</t>
+          <t>434388039.244656</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>409.775</t>
+          <t>409774941.125268</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>447.237</t>
+          <t>447237240.03243</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>430.27</t>
+          <t>430269503.169722</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>432.112</t>
+          <t>432112105.436977</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>493.645</t>
+          <t>493644654.714848</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>557.114</t>
+          <t>557113715.59472</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>566.237</t>
+          <t>566236986.070073</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>587.841</t>
+          <t>587840754.726055</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>584.676</t>
+          <t>584675969.166546</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>600.515</t>
+          <t>600514915.830102</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>550.491</t>
+          <t>550491277.769053</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1543.76</t>
+          <t>1543760094.26092</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1507.53</t>
+          <t>1507530387.70725</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1523.908</t>
+          <t>1523908173.43132</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1552.704</t>
+          <t>1552703734.94209</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1483.536</t>
+          <t>1483536185.564</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1320.929</t>
+          <t>1320928835.12217</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1310.741</t>
+          <t>1310741355.76883</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1304.777</t>
+          <t>1304777125.9957</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1413.804</t>
+          <t>1413804214.19027</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1529.928</t>
+          <t>1529928391.42415</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1586.152</t>
+          <t>1586152044.59482</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1706.266</t>
+          <t>1706265594.66168</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1902.213</t>
+          <t>1902212931.61867</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1706.561</t>
+          <t>1706561382.61726</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1233.019</t>
+          <t>1233018956.41324</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>69137.891</t>
+          <t>69137890622.9872</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72563.351</t>
+          <t>72563350591.6177</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>71730.489</t>
+          <t>71730489064.0953</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>75940.925</t>
+          <t>75940925371.9265</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>79029.83</t>
+          <t>79029830062.91</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>81929.91</t>
+          <t>81929909956.401</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>83734.743</t>
+          <t>83734742959.4298</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>82876.795</t>
+          <t>82876795132.6832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>84475.528</t>
+          <t>84475528051.0778</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>88601.155</t>
+          <t>88601155265.7151</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>89520.751</t>
+          <t>89520750737.6714</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>89640.365</t>
+          <t>89640364587.2854</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>88583.897</t>
+          <t>88583897141.0872</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>94576.604</t>
+          <t>94576603532.4986</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>91855.729</t>
+          <t>91855729290.1289</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>307.918</t>
+          <t>307917632.721007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>306.323</t>
+          <t>306322775.451278</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>265.454</t>
+          <t>265454364.567616</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>284.588</t>
+          <t>284587868.073231</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>320.289</t>
+          <t>320289484.393854</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>359.857</t>
+          <t>359857304.303819</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>297.932</t>
+          <t>297932312.20354</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>311.548</t>
+          <t>311547611.707854</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>314.687</t>
+          <t>314686645.586942</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>298.522</t>
+          <t>298521975.793562</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>279.973</t>
+          <t>279972722.266179</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>310.421</t>
+          <t>310420999.600929</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>311.623</t>
+          <t>311623252.144387</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>317.332</t>
+          <t>317331846.104873</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>276.685</t>
+          <t>276684849.760676</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22076.092</t>
+          <t>22076092003.2838</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22437.576</t>
+          <t>22437575794.902</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20820.697</t>
+          <t>20820697004.1509</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>22952.698</t>
+          <t>22952698466.9775</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24285.987</t>
+          <t>24285987446.9592</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23910.514</t>
+          <t>23910513919.3047</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>24635.514</t>
+          <t>24635514308.261</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20854.906</t>
+          <t>20854905911.9998</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25377.657</t>
+          <t>25377656549.6452</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25891.159</t>
+          <t>25891158634.1498</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>26790.494</t>
+          <t>26790493942.3431</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>26719.925</t>
+          <t>26719924528.6172</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>28150.224</t>
+          <t>28150223611.4352</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>28572.14</t>
+          <t>28572140313.9606</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>24793.926</t>
+          <t>24793925673.4268</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38028.82</t>
+          <t>38028819582.4197</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38785.166</t>
+          <t>38785166433.1023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37901.355</t>
+          <t>37901355098.7792</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>37817.125</t>
+          <t>37817124826.7129</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>36099.968</t>
+          <t>36099968439.7594</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>36566.509</t>
+          <t>36566508832.0021</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>31929.595</t>
+          <t>31929595128.7018</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30054.945</t>
+          <t>30054945442.6111</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29898.074</t>
+          <t>29898074227.0755</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30779.098</t>
+          <t>30779097916.7284</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>31708.887</t>
+          <t>31708886842.9485</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>33071.969</t>
+          <t>33071968886.2664</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35367.445</t>
+          <t>35367445361.42</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>34926.657</t>
+          <t>34926656977.9828</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>31471.37</t>
+          <t>31471369686.1096</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12370.689</t>
+          <t>12370689191.4017</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12237.21</t>
+          <t>12237209867.8947</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11557.543</t>
+          <t>11557542594.1703</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12131.335</t>
+          <t>12131334987.5267</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12077.513</t>
+          <t>12077513297.7971</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12853.017</t>
+          <t>12853016614.8317</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12854.019</t>
+          <t>12854018913.8044</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12536.046</t>
+          <t>12536045673.2458</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12346.439</t>
+          <t>12346439496.6858</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>12601.653</t>
+          <t>12601653330.9892</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>12126.151</t>
+          <t>12126150519.1717</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12094.936</t>
+          <t>12094935652.2494</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>12450.857</t>
+          <t>12450857094.9277</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>12585.847</t>
+          <t>12585847499.0148</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>10154.919</t>
+          <t>10154918886.0727</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>27818.61</t>
+          <t>27818609926.4474</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29241.6</t>
+          <t>29241600161.6656</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26007.069</t>
+          <t>26007069129.9561</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23888.336</t>
+          <t>23888335634.1439</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29615.804</t>
+          <t>29615803849.6386</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>28411.426</t>
+          <t>28411425937.1518</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28129.143</t>
+          <t>28129143033.1753</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24352.118</t>
+          <t>24352118416.3605</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23938.64</t>
+          <t>23938639675.7241</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22931.339</t>
+          <t>22931339477.5101</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22518.951</t>
+          <t>22518950618.1367</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22468.197</t>
+          <t>22468197283.4267</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>22848.388</t>
+          <t>22848387609.9032</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>22944.689</t>
+          <t>22944689053.3035</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21825.005</t>
+          <t>21825004764.6091</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>184682.789</t>
+          <t>184682789431.365</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>185736.264</t>
+          <t>185736264467.806</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>174343.962</t>
+          <t>174343962148.677</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>164412.21</t>
+          <t>164412210015.643</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>153077.847</t>
+          <t>153077847260.872</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>157373.139</t>
+          <t>157373139016.79</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>161297.995</t>
+          <t>161297994872.133</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>156658.041</t>
+          <t>156658040570.013</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>157136.821</t>
+          <t>157136820672.056</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>155130.214</t>
+          <t>155130213738.758</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>155013.072</t>
+          <t>155013072352.299</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>151629.901</t>
+          <t>151629901383.369</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>158201.429</t>
+          <t>158201429135.913</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>159598.188</t>
+          <t>159598188350.985</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>156223.027</t>
+          <t>156223026804.309</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5438.049</t>
+          <t>5438049091.38604</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5563.348</t>
+          <t>5563347929.18605</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5109.133</t>
+          <t>5109132625.63114</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4980.96</t>
+          <t>4980960046.37977</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4742.458</t>
+          <t>4742458105.1139</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4633.493</t>
+          <t>4633492926.93825</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4680.204</t>
+          <t>4680204324.22195</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4509.323</t>
+          <t>4509322937.45149</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4672.905</t>
+          <t>4672904684.85071</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4753.906</t>
+          <t>4753905979.32502</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4957.394</t>
+          <t>4957394392.17755</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5276.344</t>
+          <t>5276343893.71902</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5887.283</t>
+          <t>5887282635.14163</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5983.645</t>
+          <t>5983645337.12524</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5637.258</t>
+          <t>5637257634.17235</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2559.357</t>
+          <t>2559356892.09107</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2483.267</t>
+          <t>2483266895.51538</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2313.649</t>
+          <t>2313649074.46453</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2342.026</t>
+          <t>2342026416.82872</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2346.958</t>
+          <t>2346958246.38322</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2414.146</t>
+          <t>2414145596.35085</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2422.703</t>
+          <t>2422702790.21881</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2402.511</t>
+          <t>2402510701.1893</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2535.391</t>
+          <t>2535391035.17227</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2509.269</t>
+          <t>2509268976.28992</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2482.115</t>
+          <t>2482115370.63984</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2568.588</t>
+          <t>2568587943.23377</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2681.209</t>
+          <t>2681209339.02284</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2872.971</t>
+          <t>2872971121.26522</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2446.899</t>
+          <t>2446898980.94119</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9880.593</t>
+          <t>9880592692.78019</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9581.767</t>
+          <t>9581767136.74591</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9234.511</t>
+          <t>9234511490.77127</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9599.063</t>
+          <t>9599063467.40582</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9795.644</t>
+          <t>9795643820.22805</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10391.999</t>
+          <t>10391999477.2816</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9833.168</t>
+          <t>9833168293.31257</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9592.875</t>
+          <t>9592875012.40764</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9999.723</t>
+          <t>9999722697.60215</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10364.066</t>
+          <t>10364066170.7089</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10631.977</t>
+          <t>10631976878.5638</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10772.474</t>
+          <t>10772474040.7965</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11307.814</t>
+          <t>11307813679.0333</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>10209.09</t>
+          <t>10209090188.1298</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8507.639</t>
+          <t>8507639393.28281</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>54430.766</t>
+          <t>54430766463.7331</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>55599.55</t>
+          <t>55599549986.9759</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>56941.234</t>
+          <t>56941233509.7984</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>56323.853</t>
+          <t>56323852935.312</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>57482.559</t>
+          <t>57482559435.4395</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>57551.629</t>
+          <t>57551629121.4814</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>55350.845</t>
+          <t>55350844993.1744</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>55532.112</t>
+          <t>55532111511.5233</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>57212.766</t>
+          <t>57212765694.5843</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>60028.222</t>
+          <t>60028222421.9363</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>60129.517</t>
+          <t>60129517032.2056</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>58866.409</t>
+          <t>58866409294.3864</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>58099.016</t>
+          <t>58099015847.8877</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>62083.359</t>
+          <t>62083359453.4457</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>54526.465</t>
+          <t>54526465130.6603</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35201.902</t>
+          <t>35201902046.143</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>34282.706</t>
+          <t>34282705691.6782</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33485.581</t>
+          <t>33485580730.2434</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>32485.302</t>
+          <t>32485302326.1341</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32503.713</t>
+          <t>32503713473.7268</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>35045.388</t>
+          <t>35045388388.5817</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>31561.867</t>
+          <t>31561866733.1824</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33233.243</t>
+          <t>33233243160.8725</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>34765.031</t>
+          <t>34765031408.9777</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>38799.019</t>
+          <t>38799019165.9553</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>37529.337</t>
+          <t>37529336579.7969</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>38417.69</t>
+          <t>38417690302.8861</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>38381.297</t>
+          <t>38381296916.031</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>38688.752</t>
+          <t>38688752166.8158</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>31734.107</t>
+          <t>31734106552.5513</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>266619.569</t>
+          <t>266619568610.663</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>268050.378</t>
+          <t>268050378077.281</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>271536.469</t>
+          <t>271536469291.04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>275467.418</t>
+          <t>275467417516.574</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>284273.667</t>
+          <t>284273666932.437</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>300756.131</t>
+          <t>300756130915.549</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>286215.328</t>
+          <t>286215327522.596</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>275089.512</t>
+          <t>275089511670.755</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>279073.68</t>
+          <t>279073679794.48</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>294836.584</t>
+          <t>294836583798.267</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>304590.663</t>
+          <t>304590662628.45</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>311802.275</t>
+          <t>311802275091.805</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>301327.726</t>
+          <t>301327725818.067</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>298776.669</t>
+          <t>298776669343.293</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>250210.137</t>
+          <t>250210136889.878</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2223676.134</t>
+          <t>2223676133621.02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2279991.574</t>
+          <t>2279991574253.9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2348321.427</t>
+          <t>2348321427454.47</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2384924.128</t>
+          <t>2384924127503.2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2388326.872</t>
+          <t>2388326871793.48</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2459438.902</t>
+          <t>2459438902465.44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2544956.458</t>
+          <t>2544956458265.26</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2648052.977</t>
+          <t>2648052977146.57</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2743654.034</t>
+          <t>2743654033955.65</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2828364.163</t>
+          <t>2828364162617.91</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2906604.984</t>
+          <t>2906604983556.1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3029205.918</t>
+          <t>3029205917676.6</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3014420.286</t>
+          <t>3014420285670.6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3048789.406</t>
+          <t>3048789405721.77</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3134131.75</t>
+          <t>3134131749670.46</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7088819.631</t>
+          <t>7088819630595.23</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7211374.016</t>
+          <t>7211374016363.95</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7263378.83</t>
+          <t>7263378830057.34</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7233543.682</t>
+          <t>7233543681714.79</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7223875.682</t>
+          <t>7223875682217.95</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7382079.216</t>
+          <t>7382079216218.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7504791.33</t>
+          <t>7504791330018.61</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7592610.697</t>
+          <t>7592610696510.7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7947527.921</t>
+          <t>7947527920570</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8178276.554</t>
+          <t>8178276553846.13</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8394149.377</t>
+          <t>8394149376914.04</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8777747.824</t>
+          <t>8777747824168.48</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8849237.086</t>
+          <t>8849237086128.68</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8971026.185</t>
+          <t>8971026184985.52</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8941099.286</t>
+          <t>8941099285637.02</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
